--- a/articel table/applcaition table 36 source in SLR.xlsx
+++ b/articel table/applcaition table 36 source in SLR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef8a85349dc97480/Articles/Review Article/4. ExplainableAI/articel table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDB6EDF9-761A-4490-B618-09A00C9B008A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{EDB6EDF9-761A-4490-B618-09A00C9B008A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C24AB712-19CE-42D3-A0CB-5A15AEE4EBDE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{926FB42B-BAFB-4FE9-A68B-E585F5C1E957}"/>
   </bookViews>
@@ -916,7 +916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -929,6 +929,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1265,12 +1268,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B953AC41-827E-4EB6-AC7E-D04B4427E3E8}">
   <dimension ref="A1:J83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="30.7109375" defaultRowHeight="35.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="139.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="16384" width="30.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1302,7 +1305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="271.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1334,7 +1337,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -1398,7 +1401,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -1430,7 +1433,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -1462,7 +1465,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -1494,7 +1497,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -1526,7 +1529,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -1558,7 +1561,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1590,7 +1593,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
@@ -1622,7 +1625,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -1654,7 +1657,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="195.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>62</v>
       </c>
@@ -1686,7 +1689,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>62</v>
       </c>
@@ -1718,7 +1721,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="225.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>62</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="225.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>62</v>
       </c>
@@ -1782,7 +1785,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>82</v>
       </c>
@@ -1814,7 +1817,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>87</v>
       </c>
@@ -1846,7 +1849,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>87</v>
       </c>
@@ -1878,7 +1881,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>87</v>
       </c>
@@ -1910,7 +1913,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>87</v>
       </c>
@@ -1942,7 +1945,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>87</v>
       </c>
@@ -1974,7 +1977,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>87</v>
       </c>
@@ -2006,7 +2009,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>112</v>
       </c>
@@ -2038,7 +2041,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>118</v>
       </c>
@@ -2070,7 +2073,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="255.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>122</v>
       </c>
@@ -2102,7 +2105,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="255.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>122</v>
       </c>
@@ -2134,7 +2137,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>122</v>
       </c>
@@ -2166,7 +2169,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>122</v>
       </c>
@@ -2198,7 +2201,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>141</v>
       </c>
@@ -2230,7 +2233,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>149</v>
       </c>
@@ -2262,7 +2265,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="195.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>149</v>
       </c>
@@ -2294,7 +2297,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>160</v>
       </c>
@@ -2326,7 +2329,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>164</v>
       </c>
@@ -2358,7 +2361,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>164</v>
       </c>
@@ -2390,7 +2393,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>172</v>
       </c>
@@ -2422,7 +2425,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>172</v>
       </c>
@@ -2454,7 +2457,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>179</v>
       </c>
@@ -2486,7 +2489,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>185</v>
       </c>
@@ -2518,7 +2521,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>191</v>
       </c>
@@ -2550,7 +2553,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>195</v>
       </c>
@@ -2582,7 +2585,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>201</v>
       </c>
@@ -2614,7 +2617,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>208</v>
       </c>
@@ -2646,7 +2649,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>214</v>
       </c>
@@ -2678,7 +2681,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>220</v>
       </c>
@@ -2710,7 +2713,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>220</v>
       </c>
@@ -2742,7 +2745,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>229</v>
       </c>
@@ -2774,183 +2777,183 @@
         <v>235</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="48" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="49" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="50" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="51" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="52" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="53" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="54" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="55" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="56" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="57" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="58" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="59" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="60" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="61" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="62" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="63" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="64" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="65" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="66" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="67" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="68" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="69" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="70" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="71" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="72" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="73" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="74" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="75" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="76" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="77" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="78" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="79" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="80" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="81" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="82" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="83" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
         <v>271</v>
       </c>
     </row>
